--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487859_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487859_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9718</v>
+        <v>5.6646</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2911</v>
+        <v>4.7198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6806</v>
+        <v>0.9449</v>
       </c>
       <c r="G2" t="n">
         <v>6.2985</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2435</v>
+        <v>-0.5506</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3577</v>
+        <v>-0.9291</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1142</v>
+        <v>0.3785</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7076</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3768</v>
+        <v>1.8138</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7116</v>
+        <v>-0.0878</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3349</v>
+        <v>1.9016</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1961</v>
+        <v>-0.6908</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1429</v>
+        <v>0.6825</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0532</v>
+        <v>-1.3732</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0535</v>
+        <v>0.526</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.7971</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3716</v>
+        <v>-0.2711</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8575</v>
+        <v>-1.2168</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5391</v>
+        <v>-0.1146</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3184</v>
+        <v>-1.1022</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4437</v>
+        <v>0.0706</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1338</v>
+        <v>-0.6138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3099</v>
+        <v>0.6844</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.1852</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1852</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3185</v>
+        <v>1.0656</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2602</v>
+        <v>1.283</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5787</v>
+        <v>-0.2174</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6908</v>
+        <v>1.1961</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6825</v>
+        <v>0.1429</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3732</v>
+        <v>1.0532</v>
       </c>
       <c r="J4" t="n">
-        <v>0.526</v>
+        <v>2.0535</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7971</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2711</v>
+        <v>1.3716</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2168</v>
+        <v>-0.8575</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1146</v>
+        <v>-0.5391</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1022</v>
+        <v>-0.3184</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4247</v>
+        <v>-0.7548</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7862</v>
+        <v>-0.5624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3615</v>
+        <v>-0.1924</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1852</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2085</v>
+        <v>-0.0529</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9927</v>
+        <v>-0.7784</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7842</v>
+        <v>0.7255</v>
       </c>
       <c r="G5" t="n">
         <v>0.0263</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8057</v>
+        <v>0.9613</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3353</v>
+        <v>0.5496</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4704</v>
+        <v>0.4117</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3353</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2618</v>
+        <v>0.1249</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0736</v>
+        <v>-0.191</v>
       </c>
       <c r="G6" t="n">
         <v>-1.138</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1807</v>
+        <v>0.0886</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.901</v>
+        <v>-0.5143</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.6029</v>
       </c>
       <c r="V6" t="n">
         <v>3.2726</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.963</v>
+        <v>-0.894</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.125</v>
+        <v>-0.2322</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.838</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5991</v>
@@ -1000,13 +1000,13 @@
         <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>0.428</v>
+        <v>0.497</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4534</v>
+        <v>0.3462</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0254</v>
+        <v>0.1507</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5928</v>
+        <v>-1.2633</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6038</v>
+        <v>-1.5385</v>
       </c>
       <c r="F8" t="n">
-        <v>0.011</v>
+        <v>0.2752</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3927</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.762</v>
+        <v>-0.4325</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>-0.6524</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0443</v>
+        <v>0.2199</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0448</v>
+        <v>-3.4162</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3906</v>
+        <v>-2.9028</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6541</v>
+        <v>-0.5134</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.442</v>
+        <v>0.73</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5291</v>
+        <v>-1.7503</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9129</v>
+        <v>2.4803</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0822</v>
+        <v>3.0817</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2715</v>
+        <v>0.034</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8107</v>
+        <v>3.0477</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3598</v>
+        <v>-2.3516</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2576</v>
+        <v>-1.7842</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1022</v>
+        <v>-0.5674</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6649</v>
+        <v>-3.9542</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-5.4111</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4784</v>
+        <v>0.038</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3948</v>
+        <v>-0.5734</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8731</v>
+        <v>0.6113</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0551</v>
+        <v>-3.5858</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3995</v>
+        <v>-2.4325</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6556</v>
+        <v>-1.1533</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.9485</v>
+        <v>-3.442</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.2518</v>
+        <v>-1.5291</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6968</v>
+        <v>-1.9129</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.5605</v>
+        <v>-1.0822</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8597</v>
+        <v>-0.2715</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.7007</v>
+        <v>-0.8107</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3881</v>
+        <v>-2.3598</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3921</v>
+        <v>-1.2576</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.996</v>
+        <v>-1.1022</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6244</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3128</v>
+        <v>0.9374</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2421</v>
+        <v>-0.4367</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0706</v>
+        <v>1.374</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0437</v>
+        <v>0.5838</v>
       </c>
       <c r="W10" t="n">
         <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2112</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0938</v>
+        <v>-4.1541</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.196</v>
+        <v>-1.8746</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8978</v>
+        <v>-2.2795</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7158</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1651</v>
+        <v>0.1049</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.64</v>
+        <v>-0.3186</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8051</v>
+        <v>0.4235</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0988</v>
+        <v>-5.5106</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4385</v>
+        <v>-4.6202</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6602</v>
+        <v>-0.8905</v>
       </c>
       <c r="G12" t="n">
-        <v>0.73</v>
+        <v>-5.9485</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7503</v>
+        <v>-2.2518</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4803</v>
+        <v>-3.6968</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0817</v>
+        <v>-4.5605</v>
       </c>
       <c r="K12" t="n">
-        <v>0.034</v>
+        <v>-1.8597</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0477</v>
+        <v>-2.7007</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3516</v>
+        <v>-1.3881</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7842</v>
+        <v>-0.3921</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5674</v>
+        <v>-0.996</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.9542</v>
+        <v>0.6244</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.4111</v>
+        <v>-1.2487</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6446</v>
+        <v>0.8572</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1091</v>
+        <v>0.0215</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4645</v>
+        <v>0.8358</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.23</v>
+        <v>-1.0437</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.23</v>
+        <v>-2.2112</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.725</v>
+        <v>-10.399</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.6654</v>
+        <v>-8.3393</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0597</v>
+        <v>-2.059700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-8.676</v>
@@ -1438,7 +1438,7 @@
         <v>-10.0843</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4082</v>
+        <v>1.408199999999999</v>
       </c>
       <c r="J13" t="n">
         <v>5.695999999999999</v>
@@ -1447,19 +1447,19 @@
         <v>-0.8555999999999997</v>
       </c>
       <c r="L13" t="n">
-        <v>6.5517</v>
+        <v>6.551699999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-14.3719</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.228300000000001</v>
+        <v>-9.228299999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-5.1435</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.2027</v>
+        <v>-5.202700000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.6495</v>
@@ -1468,13 +1468,13 @@
         <v>11.4466</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4908</v>
+        <v>1.8171</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.0095</v>
+        <v>-3.6834</v>
       </c>
       <c r="U13" t="n">
-        <v>5.500100000000001</v>
+        <v>5.500299999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.6628</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8502</v>
+        <v>5.3327</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5471</v>
+        <v>2.9397</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3032</v>
+        <v>2.393</v>
       </c>
       <c r="G14" t="n">
         <v>3.9707</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7546</v>
+        <v>1.2371</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4874</v>
+        <v>-0.12</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2672</v>
+        <v>1.3571</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8247</v>
+        <v>1.8731</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5762</v>
+        <v>0.6833</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2485</v>
+        <v>1.1898</v>
       </c>
       <c r="G15" t="n">
         <v>0.4259</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.623</v>
+        <v>-0.5746</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1744</v>
+        <v>-1.0672</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5513</v>
+        <v>0.4926</v>
       </c>
       <c r="V15" t="n">
         <v>1.3975</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3539</v>
+        <v>1.4865</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0254</v>
+        <v>3.1325</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6715</v>
+        <v>-1.6461</v>
       </c>
       <c r="G16" t="n">
         <v>2.5839</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3112</v>
+        <v>-0.1786</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5219</v>
+        <v>-0.4148</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2108</v>
+        <v>0.2362</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7513</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8898</v>
+        <v>1.4095</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2372</v>
+        <v>-0.4137</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3473</v>
+        <v>1.8232</v>
       </c>
       <c r="G17" t="n">
-        <v>4.272</v>
+        <v>-0.7355</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2987</v>
+        <v>-0.3436</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9733</v>
+        <v>-0.3919</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8313</v>
+        <v>-0.3313</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4007</v>
+        <v>-0.8619</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4306</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5593</v>
+        <v>-0.4042</v>
       </c>
       <c r="N17" t="n">
-        <v>0.898</v>
+        <v>0.5183</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4573</v>
+        <v>-0.9225</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2016</v>
+        <v>0.0419</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2643</v>
+        <v>-0.3124</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4659</v>
+        <v>0.3543</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3351</v>
+        <v>0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4959</v>
+        <v>0.8677</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9495</v>
+        <v>-0.302</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4454</v>
+        <v>1.1697</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7355</v>
+        <v>-0.4026</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3436</v>
+        <v>0.1004</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3919</v>
+        <v>-0.5029</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3313</v>
+        <v>0.3896</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8619</v>
+        <v>0.3985</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5306999999999999</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4042</v>
+        <v>-0.7921</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5183</v>
+        <v>-0.2982</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9225</v>
+        <v>-0.4939</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R18" t="n">
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8716</v>
+        <v>-0.9784</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8482</v>
+        <v>-1.0672</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0235</v>
+        <v>0.0888</v>
       </c>
       <c r="V18" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4415</v>
+        <v>0.7993</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4092</v>
+        <v>0.9157</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8507</v>
+        <v>-0.1164</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4026</v>
+        <v>4.272</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1004</v>
+        <v>2.2987</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5029</v>
+        <v>1.9733</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3896</v>
+        <v>4.8313</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3985</v>
+        <v>1.4007</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.008999999999999999</v>
+        <v>3.4306</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7921</v>
+        <v>-0.5593</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2982</v>
+        <v>0.898</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4939</v>
+        <v>-1.4573</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6649</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4046</v>
+        <v>0.1111</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1744</v>
+        <v>-0.5857</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2303</v>
+        <v>0.6968</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5838</v>
+        <v>-2.3351</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2325</v>
+        <v>0.5016</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1267</v>
+        <v>-1.9124</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3591</v>
+        <v>2.4139</v>
       </c>
       <c r="G20" t="n">
         <v>0.0483</v>
@@ -2014,13 +2014,13 @@
         <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9407</v>
+        <v>-0.6716</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3701</v>
+        <v>-1.1558</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4294</v>
+        <v>0.4842</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1238</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2096</v>
+        <v>0.4539</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7985</v>
+        <v>-0.3699</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5889</v>
+        <v>0.8238</v>
       </c>
       <c r="G21" t="n">
         <v>-1.04</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5859</v>
+        <v>0.0776</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5219</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0639</v>
+        <v>0.171</v>
       </c>
       <c r="V21" t="n">
         <v>0.5838</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7474</v>
+        <v>-0.5769</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.454</v>
+        <v>-1.0525</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7066</v>
+        <v>0.4756</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.348</v>
+        <v>0.901</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.663</v>
+        <v>-0.3457</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6850000000000001</v>
+        <v>1.2467</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1053</v>
+        <v>1.2074</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5609</v>
+        <v>0.0015</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6662</v>
+        <v>1.2058</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4533</v>
+        <v>-0.3064</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1022</v>
+        <v>-0.3472</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3512</v>
+        <v>0.0408</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2655</v>
+        <v>-0.146</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0619</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2036</v>
+        <v>0.4926</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1675</v>
+        <v>-0.7076</v>
       </c>
       <c r="W22" t="n">
         <v>0.4599</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4063</v>
+        <v>-0.7078</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5882</v>
+        <v>-1.5611</v>
       </c>
       <c r="F23" t="n">
-        <v>0.182</v>
+        <v>0.8534</v>
       </c>
       <c r="G23" t="n">
-        <v>0.901</v>
+        <v>-1.348</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3457</v>
+        <v>-0.663</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2467</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2074</v>
+        <v>0.1053</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0015</v>
+        <v>-0.5609</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2058</v>
+        <v>0.6662</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3064</v>
+        <v>-1.4533</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3472</v>
+        <v>-0.1022</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0408</v>
+        <v>-1.3512</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6244</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9752999999999999</v>
+        <v>0.3052</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1744</v>
+        <v>-0.0452</v>
       </c>
       <c r="U23" t="n">
-        <v>0.199</v>
+        <v>0.3504</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="W23" t="n">
         <v>0.4599</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.7252</v>
+        <v>11.4396</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0598</v>
+        <v>2.0596</v>
       </c>
       <c r="F24" t="n">
-        <v>8.665600000000001</v>
+        <v>9.379899999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>8.675700000000003</v>
+        <v>8.675699999999999</v>
       </c>
       <c r="H24" t="n">
         <v>10.0842</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.408100000000001</v>
+        <v>-1.4081</v>
       </c>
       <c r="J24" t="n">
         <v>14.3719</v>
@@ -2311,13 +2311,13 @@
         <v>-5.6959</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8556999999999999</v>
+        <v>0.8557</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.551800000000001</v>
+        <v>-6.5518</v>
       </c>
       <c r="P24" t="n">
-        <v>5.203000000000001</v>
+        <v>5.202999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.4465</v>
@@ -2326,13 +2326,13 @@
         <v>16.6496</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.490600000000001</v>
+        <v>-0.7762999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.500300000000001</v>
+        <v>-5.5002</v>
       </c>
       <c r="U24" t="n">
-        <v>4.009499999999999</v>
+        <v>4.723999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6628</v>
@@ -2341,7 +2341,7 @@
         <v>4.6348</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.297599999999999</v>
+        <v>-6.2976</v>
       </c>
     </row>
   </sheetData>
